--- a/src/test/resources/testdata.xlsx
+++ b/src/test/resources/testdata.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="29">
   <si>
     <t xml:space="preserve">pageName</t>
   </si>
@@ -74,7 +74,34 @@
     <t xml:space="preserve">dress</t>
   </si>
   <si>
-    <t xml:space="preserve">quit</t>
+    <t xml:space="preserve">xpath=//button[@type="submit"]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scrollToElement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xpath=(//div[@class="TbCaMn"])[3]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">checkVisibilityClick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xpath=(//div[@class="TbCaMn"])[5]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">checkVisibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xpath=//*[contains(text(),'Add to cart')]</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.flipkart.com/</t>
@@ -90,7 +117,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -130,6 +157,13 @@
       <color rgb="FF0000FF"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF2A00FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -182,7 +216,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -204,6 +238,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -216,6 +254,66 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF2A00FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -224,12 +322,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30.28"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -339,27 +437,30 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="0" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E8" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>17</v>
+      <c r="C9" s="3"/>
+      <c r="D9" s="0" t="n">
+        <v>5000</v>
       </c>
       <c r="E9" s="0" t="s">
         <v>8</v>
@@ -367,7 +468,13 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>5</v>
+        <v>18</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>20</v>
       </c>
       <c r="E10" s="0" t="s">
         <v>8</v>
@@ -375,7 +482,13 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>5</v>
+        <v>18</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>2000</v>
       </c>
       <c r="E11" s="0" t="s">
         <v>8</v>
@@ -383,11 +496,48 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>5</v>
+        <v>18</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
         <v>5</v>
       </c>
     </row>
@@ -408,7 +558,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -425,11 +575,11 @@
       <c r="A2" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>18</v>
+      <c r="B2" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
